--- a/Data/Building/MeetingRoomTwo.Brightness.xlsx
+++ b/Data/Building/MeetingRoomTwo.Brightness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:I322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709260126</v>
+        <v>1711852424</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709260148</v>
+        <v>1711852447</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709260175</v>
+        <v>1711852471</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709260925</v>
+        <v>1711853045</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709260965</v>
+        <v>1711853084</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709260991</v>
+        <v>1711853118</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709261022</v>
+        <v>1711853156</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709261059</v>
+        <v>1711853181</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709261087</v>
+        <v>1711853208</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709274325</v>
+        <v>1711854430</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709274363</v>
+        <v>1711854454</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709274391</v>
+        <v>1711854485</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709274422</v>
+        <v>1711859516</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709274449</v>
+        <v>1711859547</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709274474</v>
+        <v>1711859580</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,11 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709253342</v>
+        <v>1711866484</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1005,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1024,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709253367</v>
+        <v>1711866514</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1038,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1057,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709253394</v>
+        <v>1711866530</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1071,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1090,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709253428</v>
+        <v>1711866558</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1104,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709253462</v>
+        <v>1711866585</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1137,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1156,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709254896</v>
+        <v>1711866620</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1166,15 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709254918</v>
+        <v>1711868878</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1203,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1226,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709254947</v>
+        <v>1711868908</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1240,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1259,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709254971</v>
+        <v>1711868931</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1269,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1292,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709254996</v>
+        <v>1711868961</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1302,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1325,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709266128</v>
+        <v>1711868994</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1358,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709266155</v>
+        <v>1711869038</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1368,15 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709266194</v>
+        <v>1711932151</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1405,11 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1428,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709266231</v>
+        <v>1711932183</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1442,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1461,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709266261</v>
+        <v>1711932203</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1471,11 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1494,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709266288</v>
+        <v>1711932224</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1504,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1527,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709267679</v>
+        <v>1711932256</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1541,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1560,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709267708</v>
+        <v>1711932328</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1570,15 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1597,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709267742</v>
+        <v>1711944885</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1607,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1630,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709267770</v>
+        <v>1711944925</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1644,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1663,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709267799</v>
+        <v>1711944957</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1673,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1696,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709267837</v>
+        <v>1711944983</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1706,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1729,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709341579</v>
+        <v>1711945026</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1743,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1762,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709341608</v>
+        <v>1711945054</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1772,15 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709341631</v>
+        <v>1712019720</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1809,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1832,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709341664</v>
+        <v>1712019760</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1846,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1865,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709341691</v>
+        <v>1712019803</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1875,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1898,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709341723</v>
+        <v>1712019847</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1908,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1931,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709354491</v>
+        <v>1712019868</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1945,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1964,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709354525</v>
+        <v>1712019890</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1974,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1997,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709354547</v>
+        <v>1712033837</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2007,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2030,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709354576</v>
+        <v>1712033878</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2044,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2063,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709354613</v>
+        <v>1712033902</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2073,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2096,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709354662</v>
+        <v>1712033933</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2106,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2129,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709427246</v>
+        <v>1712033972</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2143,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2162,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709427276</v>
+        <v>1712034002</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2172,15 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2199,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709427299</v>
+        <v>1712106996</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2209,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2232,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709427330</v>
+        <v>1712107019</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2246,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2265,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709427353</v>
+        <v>1712107044</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2275,11 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2298,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709427378</v>
+        <v>1712107084</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2308,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709439642</v>
+        <v>1712107114</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2345,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2364,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709439669</v>
+        <v>1712107141</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2374,15 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2401,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709439702</v>
+        <v>1712120458</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2411,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2434,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709440856</v>
+        <v>1712120478</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2448,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2467,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709440879</v>
+        <v>1712120501</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2477,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2500,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709440900</v>
+        <v>1712120534</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2510,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2533,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709441694</v>
+        <v>1712120569</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2547,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2566,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709441733</v>
+        <v>1712120594</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2576,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2599,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709441759</v>
+        <v>1712121805</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2609,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2632,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709441790</v>
+        <v>1712121828</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2646,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2665,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709441824</v>
+        <v>1712121862</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2675,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2698,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709441859</v>
+        <v>1712121899</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2708,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2731,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709513094</v>
+        <v>1712121935</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2745,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2764,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709513138</v>
+        <v>1712121966</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2774,15 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2801,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709513159</v>
+        <v>1712190985</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2811,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2834,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709513192</v>
+        <v>1712191003</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2848,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2867,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709513235</v>
+        <v>1712191028</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2877,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2900,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709513277</v>
+        <v>1712191052</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2910,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2933,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709514520</v>
+        <v>1712191073</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2947,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2966,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709514537</v>
+        <v>1712191100</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2976,15 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3003,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709514565</v>
+        <v>1712206630</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3013,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3036,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709514599</v>
+        <v>1712206658</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3050,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3069,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709514629</v>
+        <v>1712206682</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3079,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3102,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709514655</v>
+        <v>1712206716</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3112,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3135,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709525658</v>
+        <v>1712206748</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3149,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3168,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709525677</v>
+        <v>1712206782</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3178,15 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3205,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709525703</v>
+        <v>1712278928</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3215,11 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3238,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709526753</v>
+        <v>1712278949</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3252,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3271,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709526778</v>
+        <v>1712278971</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3281,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3304,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709526817</v>
+        <v>1712279015</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3314,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3337,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709528282</v>
+        <v>1712279042</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3351,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3370,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709528316</v>
+        <v>1712279065</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3380,15 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3407,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709528343</v>
+        <v>1712290957</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3417,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3440,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709528384</v>
+        <v>1712290986</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3454,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3473,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709591320</v>
+        <v>1712291018</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3483,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3506,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709597780</v>
+        <v>1712294376</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3516,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3539,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709601252</v>
+        <v>1712356729</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3553,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3572,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709601272</v>
+        <v>1712363725</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3582,15 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3609,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709601288</v>
+        <v>1712539426</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3619,11 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3642,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709601315</v>
+        <v>1712539469</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3656,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3675,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709601349</v>
+        <v>1712539487</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3685,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3708,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709601388</v>
+        <v>1712540010</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3718,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3741,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709617212</v>
+        <v>1712540042</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3755,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3774,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709617226</v>
+        <v>1712540082</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3784,15 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3811,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709617244</v>
+        <v>1712549262</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3821,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3844,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709617271</v>
+        <v>1712549290</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3858,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3877,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709678108</v>
+        <v>1712549315</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3887,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3910,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709685086</v>
+        <v>1712549347</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3920,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3943,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709857153</v>
+        <v>1712549369</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3957,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3976,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709857181</v>
+        <v>1712549396</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +3986,15 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4013,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709857211</v>
+        <v>1712551459</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4023,11 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4046,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709857243</v>
+        <v>1712551491</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4060,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4079,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709857288</v>
+        <v>1712551517</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4089,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4112,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709857324</v>
+        <v>1712551545</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3953,10 +4122,11 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4145,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709869511</v>
+        <v>1712551582</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4159,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4178,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709869546</v>
+        <v>1712551611</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4188,15 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4215,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709869581</v>
+        <v>1712626005</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4225,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4248,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709869630</v>
+        <v>1712626024</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4262,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4281,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709869655</v>
+        <v>1712626053</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4291,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4314,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709869695</v>
+        <v>1712626093</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4324,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4347,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709946793</v>
+        <v>1712626125</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4361,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4380,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709946815</v>
+        <v>1712626145</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4390,15 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4417,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1709946833</v>
+        <v>1712638338</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4427,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4450,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1709946865</v>
+        <v>1712638365</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4464,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4483,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1709946891</v>
+        <v>1712638401</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4305,10 +4493,11 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4516,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1709946938</v>
+        <v>1712638446</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4526,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4549,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1709957803</v>
+        <v>1712638490</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4563,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4582,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1709957827</v>
+        <v>1712638524</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4592,15 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4619,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1709957851</v>
+        <v>1712711671</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4629,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4652,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1709957878</v>
+        <v>1712711694</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4666,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4685,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1709957911</v>
+        <v>1712711714</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4695,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4718,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1709957933</v>
+        <v>1712711734</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4728,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4751,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710033939</v>
+        <v>1712711764</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4765,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4784,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710033963</v>
+        <v>1712711796</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4794,15 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4821,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710033997</v>
+        <v>1712714188</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4831,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4854,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710034040</v>
+        <v>1712714226</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4868,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4887,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710034084</v>
+        <v>1712714264</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4897,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4920,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710034116</v>
+        <v>1712714293</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4930,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4953,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710045743</v>
+        <v>1712714320</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4967,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4986,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710045769</v>
+        <v>1712714349</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +4996,15 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5023,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710045804</v>
+        <v>1712724012</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5033,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5056,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710045828</v>
+        <v>1712724052</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5070,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5089,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710045858</v>
+        <v>1712724085</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5099,11 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5122,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710045885</v>
+        <v>1712724127</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5132,11 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5155,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710049015</v>
+        <v>1712724177</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5169,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5188,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710049054</v>
+        <v>1712724210</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5198,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5221,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710049074</v>
+        <v>1712725748</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5231,11 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5254,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710049107</v>
+        <v>1712725777</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5268,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5287,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710049139</v>
+        <v>1712725803</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5297,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5320,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710049168</v>
+        <v>1712725840</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5330,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5353,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710120314</v>
+        <v>1712725864</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5367,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5386,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710120350</v>
+        <v>1712725901</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5396,15 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5423,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710120377</v>
+        <v>1712799272</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5433,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5456,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710126276</v>
+        <v>1712799315</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5470,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5489,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710126329</v>
+        <v>1712799342</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5499,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5522,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710126363</v>
+        <v>1712799889</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5532,11 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5555,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710134099</v>
+        <v>1712799917</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5569,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5588,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710134127</v>
+        <v>1712799942</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5598,15 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5625,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710134162</v>
+        <v>1712808858</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5635,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5658,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710134191</v>
+        <v>1712808884</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5672,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5691,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710134232</v>
+        <v>1712808923</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5701,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5724,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710134295</v>
+        <v>1712808972</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5734,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5757,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710205568</v>
+        <v>1712809008</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5771,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5790,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710205601</v>
+        <v>1712809049</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5800,15 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5827,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710205631</v>
+        <v>1712810725</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5837,11 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5860,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710205950</v>
+        <v>1712810751</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5874,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5893,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710205983</v>
+        <v>1712810777</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5903,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5926,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710206025</v>
+        <v>1712810806</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +5936,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5959,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710220582</v>
+        <v>1712810838</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5973,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5992,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710220608</v>
+        <v>1712810887</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +6002,15 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6029,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710220635</v>
+        <v>1712885719</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +6039,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6062,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710220675</v>
+        <v>1712885746</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6076,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6095,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710220706</v>
+        <v>1712885769</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6105,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6128,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710220742</v>
+        <v>1712885799</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6138,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6161,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710464665</v>
+        <v>1712885836</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6175,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6194,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710464682</v>
+        <v>1712885863</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5937,10 +6204,15 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6231,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710464722</v>
+        <v>1712897856</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5969,10 +6241,11 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6264,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710464752</v>
+        <v>1712897881</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6278,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6297,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710464794</v>
+        <v>1712897895</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6307,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6330,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710464828</v>
+        <v>1712897931</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6340,11 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6363,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710475948</v>
+        <v>1712897966</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6377,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6396,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710475991</v>
+        <v>1712897992</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6406,15 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6433,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710476025</v>
+        <v>1713141544</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6443,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6466,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710476061</v>
+        <v>1713141560</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6480,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6499,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710476095</v>
+        <v>1713141601</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6225,10 +6509,11 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6532,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710476164</v>
+        <v>1713141647</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6542,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6565,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710549624</v>
+        <v>1713141695</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6579,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6598,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710549649</v>
+        <v>1713141752</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6321,10 +6608,15 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6635,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710549681</v>
+        <v>1713154283</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6645,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6668,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710549704</v>
+        <v>1713154304</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6682,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6701,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710549761</v>
+        <v>1713154334</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6711,11 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6734,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710549793</v>
+        <v>1713154360</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6744,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6767,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710564904</v>
+        <v>1713154385</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6781,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6800,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710564944</v>
+        <v>1713154418</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6513,10 +6810,15 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6837,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710564986</v>
+        <v>1713227874</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6847,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6870,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710565030</v>
+        <v>1713227902</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6884,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6903,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710565059</v>
+        <v>1713227930</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6913,11 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6936,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710635594</v>
+        <v>1713227958</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6946,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6969,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710639265</v>
+        <v>1713227987</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6983,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +7002,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710639298</v>
+        <v>1713228023</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +7012,15 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7039,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710639328</v>
+        <v>1713239205</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +7049,11 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7072,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710639366</v>
+        <v>1713239220</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7086,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7105,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710639406</v>
+        <v>1713239243</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6801,10 +7115,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7138,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710639436</v>
+        <v>1713239274</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6833,10 +7148,11 @@
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7171,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710651407</v>
+        <v>1713239325</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7185,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7204,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710651437</v>
+        <v>1713239357</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7214,15 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7241,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710651464</v>
+        <v>1713316054</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7251,11 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7274,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710653959</v>
+        <v>1713316085</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7288,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7307,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710714317</v>
+        <v>1713316108</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6993,10 +7317,11 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7340,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710720237</v>
+        <v>1713316136</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7025,10 +7350,11 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7373,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710724064</v>
+        <v>1713316176</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7387,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7406,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710724103</v>
+        <v>1713316212</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7089,10 +7416,15 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7443,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710724136</v>
+        <v>1713325595</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7121,10 +7453,11 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7476,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710724171</v>
+        <v>1713325625</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7490,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7509,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710724208</v>
+        <v>1713325668</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7519,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7542,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710724235</v>
+        <v>1713326167</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7217,10 +7552,11 @@
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7575,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710736487</v>
+        <v>1713326207</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7589,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7608,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710736526</v>
+        <v>1713326243</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7618,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7641,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710736584</v>
+        <v>1713327095</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7313,10 +7651,11 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7674,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710736614</v>
+        <v>1713327133</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7688,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7707,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710736658</v>
+        <v>1713327169</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,10 +7717,11 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7740,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710736690</v>
+        <v>1713327187</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7409,10 +7750,11 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7773,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710810992</v>
+        <v>1713327213</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7787,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7806,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710811020</v>
+        <v>1713327242</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7473,10 +7816,15 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7843,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710811055</v>
+        <v>1713399540</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7505,10 +7853,11 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7876,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710811083</v>
+        <v>1713399582</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +7890,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7909,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710811119</v>
+        <v>1713399608</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7569,10 +7919,11 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7942,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710811155</v>
+        <v>1713399659</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7601,10 +7952,11 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7975,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710823383</v>
+        <v>1713399687</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7989,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +8008,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710823414</v>
+        <v>1713399703</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7665,10 +8018,15 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +8045,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710823451</v>
+        <v>1713409915</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7697,10 +8055,11 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8078,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710823475</v>
+        <v>1713409957</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7733,6 +8092,7 @@
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8111,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710823510</v>
+        <v>1713409979</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7761,10 +8121,11 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8144,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710823547</v>
+        <v>1713410105</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7793,10 +8154,11 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8177,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711069247</v>
+        <v>1713410132</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7829,6 +8191,7 @@
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8210,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711069268</v>
+        <v>1713410162</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7857,10 +8220,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8243,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711069303</v>
+        <v>1713411070</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7889,10 +8253,11 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8276,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711069342</v>
+        <v>1713411092</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8290,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8309,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711069378</v>
+        <v>1713411112</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7953,10 +8319,11 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8342,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711069405</v>
+        <v>1713487308</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7985,10 +8352,11 @@
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8375,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711081126</v>
+        <v>1713487336</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8021,6 +8389,7 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8408,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711081157</v>
+        <v>1713487366</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8049,10 +8418,11 @@
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8441,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711081182</v>
+        <v>1713488082</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8081,10 +8451,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8474,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711081214</v>
+        <v>1713488110</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8117,6 +8488,7 @@
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8507,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711081235</v>
+        <v>1713488131</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8145,10 +8517,11 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8540,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711081270</v>
+        <v>1713488143</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8177,10 +8550,11 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8573,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711082538</v>
+        <v>1713488166</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8213,6 +8587,7 @@
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8606,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711082565</v>
+        <v>1713488191</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8241,10 +8616,15 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8643,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711082594</v>
+        <v>1713500020</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8273,10 +8653,11 @@
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8676,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711153811</v>
+        <v>1713500048</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8690,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8709,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711153846</v>
+        <v>1713500082</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8337,10 +8719,11 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8742,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711153868</v>
+        <v>1713500117</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8369,10 +8752,11 @@
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8775,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711155281</v>
+        <v>1713500138</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8789,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8808,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711155292</v>
+        <v>1713500167</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8433,10 +8818,15 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8845,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711155313</v>
+        <v>1713746481</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8465,10 +8855,11 @@
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8878,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711155354</v>
+        <v>1713746511</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8501,6 +8892,7 @@
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8911,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711155375</v>
+        <v>1713746533</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8529,10 +8921,11 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8944,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711155405</v>
+        <v>1713746587</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8561,10 +8954,11 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8977,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711170056</v>
+        <v>1713746616</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8991,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +9010,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711170080</v>
+        <v>1713746662</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8625,10 +9020,15 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +9047,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711170098</v>
+        <v>1713755575</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8657,10 +9057,11 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +9080,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711170140</v>
+        <v>1713755638</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8693,6 +9094,7 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8711,7 +9113,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711170165</v>
+        <v>1713755696</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8721,10 +9123,11 @@
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8743,7 +9146,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711170205</v>
+        <v>1713832756</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8753,10 +9156,11 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8775,7 +9179,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711240775</v>
+        <v>1713832808</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8789,6 +9193,7 @@
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8807,7 +9212,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711240830</v>
+        <v>1713832838</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8817,10 +9222,11 @@
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8839,7 +9245,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711240869</v>
+        <v>1713834640</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8849,10 +9255,11 @@
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8871,7 +9278,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711240896</v>
+        <v>1713834668</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8885,6 +9292,7 @@
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8903,7 +9311,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1711240919</v>
+        <v>1713834684</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8913,10 +9321,11 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8935,7 +9344,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1711240960</v>
+        <v>1713834714</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8945,10 +9354,11 @@
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8967,7 +9377,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1711242019</v>
+        <v>1713834752</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8981,6 +9391,7 @@
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8999,7 +9410,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1711242040</v>
+        <v>1713834787</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -9009,10 +9420,15 @@
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9031,7 +9447,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1711242071</v>
+        <v>1713846753</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9041,10 +9457,11 @@
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9063,7 +9480,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1711242103</v>
+        <v>1713846784</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9077,6 +9494,7 @@
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9095,7 +9513,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1711242146</v>
+        <v>1713846813</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9105,10 +9523,11 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9127,7 +9546,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1711242184</v>
+        <v>1713846850</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -9137,10 +9556,11 @@
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9159,7 +9579,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1711254981</v>
+        <v>1713846879</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -9173,6 +9593,7 @@
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9191,7 +9612,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1711255007</v>
+        <v>1713846920</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -9201,10 +9622,15 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9223,7 +9649,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1711255031</v>
+        <v>1713848010</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9233,10 +9659,11 @@
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9255,7 +9682,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1711255072</v>
+        <v>1713848039</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9269,6 +9696,7 @@
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9287,7 +9715,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1711255112</v>
+        <v>1713848070</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -9297,10 +9725,11 @@
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9319,7 +9748,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1711255153</v>
+        <v>1713848098</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9329,10 +9758,11 @@
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9351,7 +9781,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1711327750</v>
+        <v>1713848134</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -9365,6 +9795,7 @@
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9383,7 +9814,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1711327789</v>
+        <v>1713848164</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -9393,10 +9824,15 @@
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9415,7 +9851,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1711327812</v>
+        <v>1713919630</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -9425,10 +9861,11 @@
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9447,7 +9884,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1711327838</v>
+        <v>1713919663</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -9461,6 +9898,7 @@
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9479,7 +9917,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1711327870</v>
+        <v>1713919693</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -9489,10 +9927,11 @@
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9511,7 +9950,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1711327905</v>
+        <v>1713919721</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -9521,10 +9960,11 @@
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9543,7 +9983,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1711340830</v>
+        <v>1713919749</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -9557,6 +9997,7 @@
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9575,7 +10016,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1711340871</v>
+        <v>1713919781</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9585,10 +10026,15 @@
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9607,7 +10053,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1711340906</v>
+        <v>1713932948</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -9617,10 +10063,11 @@
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9639,7 +10086,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1711340939</v>
+        <v>1713932982</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9653,6 +10100,7 @@
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9671,7 +10119,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1711340985</v>
+        <v>1713933018</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9681,10 +10129,11 @@
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9703,7 +10152,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1711341022</v>
+        <v>1713933068</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9713,10 +10162,11 @@
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9735,7 +10185,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1711416106</v>
+        <v>1713933107</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9749,6 +10199,7 @@
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9767,7 +10218,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1711416143</v>
+        <v>1713933128</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9777,10 +10228,15 @@
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9799,7 +10255,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1711416173</v>
+        <v>1714003532</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9809,10 +10265,11 @@
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9831,7 +10288,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1711416205</v>
+        <v>1714003548</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9845,6 +10302,7 @@
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9863,7 +10321,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1711416233</v>
+        <v>1714003572</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9873,10 +10331,11 @@
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9895,7 +10354,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1711416287</v>
+        <v>1714003607</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9905,10 +10364,11 @@
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9927,7 +10387,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1711429282</v>
+        <v>1714003626</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9941,6 +10401,7 @@
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9959,7 +10420,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1711429319</v>
+        <v>1714003652</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9969,10 +10430,11 @@
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9991,7 +10453,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1711429341</v>
+        <v>1714016701</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -10001,10 +10463,782 @@
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1714016722</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1714016751</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
           <t>MeetingRoomTwo.Brightness.state: Dark</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1714016798</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1714085680</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1714089538</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1714090500</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1714090528</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1714090562</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1714090598</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1714090624</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1714090665</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1714100388</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1714100418</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1714100455</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1714100489</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1714100520</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1714100549</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1714103054</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1714103085</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1714103110</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1714103136</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1714170135</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1714177242</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
